--- a/src/attributions/attributions_ig_traj_79.xlsx
+++ b/src/attributions/attributions_ig_traj_79.xlsx
@@ -1568,46 +1568,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.002069964128266359</v>
+        <v>0.01325284978527766</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07730603588121533</v>
+        <v>0.03955790533322447</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.05551418413442984</v>
+        <v>-0.04359999967620309</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.009083541316800293</v>
+        <v>0.08807095378349462</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01697575596576852</v>
+        <v>0.006252224237753859</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.01640461887214877</v>
+        <v>-0.008082650344652552</v>
       </c>
       <c r="O3" t="n">
         <v>-0</v>
@@ -1619,22 +1619,22 @@
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05427314496516586</v>
+        <v>-0.03949005234717801</v>
       </c>
       <c r="T3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.05155039147134274</v>
+        <v>0.02335286984406456</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.09298851497150744</v>
+        <v>-0.06413110720172835</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -1646,103 +1646,103 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01238805772666</v>
+        <v>0.009975358058685463</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.003398114577732756</v>
+        <v>-0.01895823313469672</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.05492225655699179</v>
+        <v>-0.01142469309181158</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.0388527198309391</v>
+        <v>0.01555843543262201</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.03176712440891678</v>
+        <v>-0.04066610291624673</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.1207807400132129</v>
+        <v>-0.1342400995950091</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
         <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.1152370085230348</v>
+        <v>-0.1141943513808276</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2873696199930608</v>
+        <v>0.03659898880240619</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.3363794964688445</v>
+        <v>-0.1878541897985944</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.01855774847325415</v>
+        <v>0.00975368106521516</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.007297624151052958</v>
+        <v>0.001545494539973221</v>
       </c>
       <c r="BF3" t="n">
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-3.47176202891753e-11</v>
+        <v>3.935718501488178e-11</v>
       </c>
       <c r="BH3" t="n">
         <v>-0</v>
@@ -1754,28 +1754,28 @@
         <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.04634542842465059</v>
+        <v>0.03885468478329988</v>
       </c>
       <c r="BM3" t="n">
         <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.03649186163449025</v>
+        <v>-0.005956671276592456</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.2515602159880996</v>
+        <v>0.06879637578975324</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1784,49 +1784,49 @@
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.1155580703458693</v>
+        <v>-0.1226339691670737</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.186746107549376</v>
+        <v>0.09184556766168753</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.05163451517973797</v>
+        <v>-0.1074750753407873</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
         <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.02283547039429726</v>
+        <v>0.06068541993839287</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.02329961142607408</v>
+        <v>-0.0230119971444013</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.08275822443372252</v>
+        <v>0.08163243110761996</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ3" t="n">
         <v>0</v>
@@ -1835,22 +1835,22 @@
         <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.03827267371274347</v>
+        <v>0.005330397071162325</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1063984401100928</v>
+        <v>-0.01912866552024967</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.2678938949066166</v>
+        <v>-0.05756288799937954</v>
       </c>
       <c r="CR3" t="n">
         <v>-0</v>
@@ -1859,31 +1859,31 @@
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
         <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.03754105600361694</v>
+        <v>0.0560935620054332</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.003801337771822307</v>
+        <v>-0.03424014724337684</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.02989260526968161</v>
+        <v>0.04216974300269443</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1892,49 +1892,49 @@
         <v>-0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.02903088405338915</v>
+        <v>0.04194509211432052</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.0008790382051082053</v>
+        <v>0.0003648629220030951</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.1102366426172665</v>
+        <v>0.1655597081117747</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
         <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.02386010882651828</v>
+        <v>0.05469300064458304</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.04398207561702164</v>
+        <v>0.02096402943392632</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.3382472396547309</v>
+        <v>-0.0773772999754066</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
         <v>0</v>
@@ -1943,52 +1943,52 @@
         <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.03892509997138652</v>
+        <v>0.001874095088579786</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.02627335904324897</v>
+        <v>0.08802333153764123</v>
       </c>
       <c r="DZ3" t="n">
         <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.02272788147958179</v>
+        <v>-0.05457922847995179</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.04026193953342115</v>
+        <v>0.03732053729853056</v>
       </c>
       <c r="EG3" t="n">
         <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.06002449346425735</v>
+        <v>0.0006154929387923308</v>
       </c>
       <c r="EI3" t="n">
         <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.05909441359448681</v>
+        <v>0.06190901018781319</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
@@ -2000,49 +2000,49 @@
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.002142135921175633</v>
+        <v>0.008738871874146325</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.02398049520044081</v>
+        <v>-0.003162326933742255</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.1192344149786673</v>
+        <v>0.09035183404120628</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.01593240078203653</v>
+        <v>0.06183533612458635</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0.02177870998722519</v>
+        <v>-0.04185744985748974</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.01759674557926716</v>
+        <v>0.05313519910323011</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
@@ -2051,25 +2051,25 @@
         <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.09842575321618323</v>
+        <v>0.1726415956350174</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.01269475722697834</v>
+        <v>-0.01557415069095604</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.004904345487090264</v>
+        <v>0.05816727620044022</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
         <v>-0</v>
@@ -2081,19 +2081,19 @@
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.06852537564677995</v>
+        <v>0.1307149567655512</v>
       </c>
       <c r="FQ3" t="n">
         <v>-0</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.002105425209316271</v>
+        <v>0.001033127943896974</v>
       </c>
       <c r="FS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.008032569056219184</v>
+        <v>0.006598342586878266</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
@@ -2108,13 +2108,13 @@
         <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.03817143150279223</v>
+        <v>0.09632073098167754</v>
       </c>
       <c r="FZ3" t="n">
         <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.0334123276025968</v>
+        <v>0.0008542162479593556</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
@@ -2123,33 +2123,33 @@
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1260114947908236</v>
+        <v>0.06323295548491274</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.009662670357743453</v>
+        <v>-0.005974858570100573</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.02573749440525783</v>
+        <v>-0.008330251446556077</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2161,22 +2161,22 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0476560525878232</v>
+        <v>0.03380141259777038</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05203006481278094</v>
+        <v>0.03906487040960252</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0101951128422844</v>
+        <v>-0.002902233605651308</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -2188,85 +2188,85 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1175643477557879</v>
+        <v>0.03271316005201669</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02892492860803549</v>
+        <v>-0.02335811620737571</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04452901012922662</v>
+        <v>-0.01086106219911585</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0097016863187975</v>
+        <v>-0.006312334198118187</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.00602879647078078</v>
+        <v>-0.00525562255202171</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.004280075581267477</v>
+        <v>-0.01397893307569911</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.04701143132458584</v>
+        <v>0.05941985231194111</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.0513787448180457</v>
+        <v>-0.01624844302193059</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01046168606032955</v>
+        <v>0.02434375106415582</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,25 +2275,25 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.3198575407838974</v>
+        <v>0.15300073224467</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.006760600318228204</v>
+        <v>-0.03274033780948057</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1653931571032944</v>
+        <v>-0.04951391300602635</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
         <v>-0</v>
@@ -2302,16 +2302,16 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.06947597121313e-05</v>
+        <v>-0.004802701661782404</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.01355032232453316</v>
+        <v>-0.002836329186593608</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.01134724472393804</v>
+        <v>-0.002499276769114359</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2320,31 +2320,31 @@
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.008335797916364192</v>
+        <v>-0.0001455031380098415</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.07636120787944549</v>
+        <v>0.01394417115989085</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.02026126456238179</v>
+        <v>0.03258993870998656</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,25 +2356,25 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1819856137558718</v>
+        <v>0.1084071435644312</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01379297029039224</v>
+        <v>-0.03399484053219127</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.01666628129074117</v>
+        <v>0.002441030667293066</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
@@ -2383,46 +2383,46 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.05694917590815388</v>
+        <v>-0.04830225742216371</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.005758269194254879</v>
+        <v>0.03725283547422285</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.01117884239134413</v>
+        <v>0.003268191988587104</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.01771290942811918</v>
+        <v>-0.03177149689259341</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.09202229382103436</v>
+        <v>0.04896237879227553</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.1254234315241177</v>
+        <v>0.03495452788046848</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
@@ -2434,52 +2434,52 @@
         <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.04831474738370208</v>
+        <v>-0.0517334520813606</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.03284156118049429</v>
+        <v>0.0425867019849572</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.008533857924130592</v>
+        <v>0.004776120054111247</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.05382874944581958</v>
+        <v>-0.02576518182328132</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0.002053579691642214</v>
+        <v>-0.002845802927393872</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.0003833074086478124</v>
+        <v>0.0006032063723790377</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
@@ -2491,25 +2491,25 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.06933734875670172</v>
+        <v>-0.02622391674369562</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.03010762985802248</v>
+        <v>0.006320759873135239</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.009149246580673365</v>
+        <v>-0.02562502906983903</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
@@ -2518,16 +2518,16 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.05241039659219321</v>
+        <v>0.02120634212529175</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.04835191911138539</v>
+        <v>0.0317319781662742</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.01266203700316218</v>
+        <v>-0.009300321256164916</v>
       </c>
       <c r="EB4" t="n">
         <v>-0</v>
@@ -2539,55 +2539,55 @@
         <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.02530289227103139</v>
+        <v>-0.0360287809729254</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.05019258330724011</v>
+        <v>0.02911224965070046</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0004772769007957415</v>
+        <v>0.00683529914472599</v>
       </c>
       <c r="EK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.02547476399030501</v>
+        <v>-0.02748771486816399</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.019094689658602</v>
+        <v>-0.03694336422507799</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.004423107653390027</v>
+        <v>0.003369392176578675</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
@@ -2596,76 +2596,76 @@
         <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.04767739865458311</v>
+        <v>-0.05635736201732287</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.01549405592980067</v>
+        <v>0.04032098597073685</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.02363100167072272</v>
+        <v>-7.450006057087599e-05</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.01829216507156253</v>
+        <v>-0.02392780574970092</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.05143802225075154</v>
+        <v>0.006610511421778185</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01496764869393172</v>
+        <v>0.0003382032847898255</v>
       </c>
       <c r="FL4" t="n">
         <v>0</v>
       </c>
       <c r="FM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN4" t="n">
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.0007244557124185597</v>
+        <v>0.0009705728644839353</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>-0.004840335622916803</v>
+        <v>0.05962280225772702</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.000221453013849919</v>
+        <v>-0.0004729134510196823</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2677,28 +2677,28 @@
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.005466246941602855</v>
+        <v>-0.04345968024348109</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.01839361296042817</v>
+        <v>0.02202978544031777</v>
       </c>
       <c r="GC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
         <v>-0</v>
@@ -2709,25 +2709,25 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02907946648336207</v>
+        <v>0.1327505795785336</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03420953671561638</v>
+        <v>0.03043125305026551</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01560792299331791</v>
+        <v>-0.04252984602555183</v>
       </c>
       <c r="G5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,34 +2736,34 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005426016630978602</v>
+        <v>0.09157510920602328</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01478310193251512</v>
+        <v>-0.003217848767713569</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002535101630181633</v>
+        <v>0.007303896869003433</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.00472525982889273</v>
+        <v>0.06980404159471561</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2772,16 +2772,16 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.02873850651399533</v>
+        <v>-0.06147939860303406</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01951980903030176</v>
+        <v>0.02675100995546467</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>-0</v>
@@ -2790,34 +2790,34 @@
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.005332744576224444</v>
+        <v>-0.007590700814410772</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.003217175285277128</v>
+        <v>-0.02920541401247545</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.002303257828563927</v>
+        <v>-0.004045166678397182</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01477004793606018</v>
+        <v>0.06116242821000012</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -2826,37 +2826,37 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.02286141242175585</v>
+        <v>0.04541663285874677</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.00528341593377739</v>
+        <v>-0.05904143719875936</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.05235485818530593</v>
+        <v>0.2572488388937263</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.06756682493265274</v>
+        <v>-0.0800597969977053</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.02147576058587886</v>
+        <v>-0.1069421665879756</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2865,28 +2865,28 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.005341835144999829</v>
+        <v>0.001345917943126777</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.004443883786083144</v>
+        <v>-0.002048884754023146</v>
       </c>
       <c r="BH5" t="n">
-        <v>-5.270323006035491e-12</v>
+        <v>-1.965696266083108e-11</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2895,28 +2895,28 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.03875215380941478</v>
+        <v>0.005364506363077978</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.01709005462848133</v>
+        <v>0.06459165362114906</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.01113922962321014</v>
+        <v>0.06826551208288542</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.02411137280529653</v>
+        <v>0.2282630306711932</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,13 +2934,13 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.02592504116250154</v>
+        <v>0.005946107240267615</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.005219052721342151</v>
+        <v>-0.04495509350748252</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
@@ -2952,22 +2952,22 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.004328461004174031</v>
+        <v>-0.07793413588338621</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01607802517909928</v>
+        <v>-0.02992975935884533</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01564585757088842</v>
+        <v>0.05170799588024642</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
@@ -2976,55 +2976,55 @@
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.005063086314535479</v>
+        <v>-0.07141232328038125</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.003722579925383168</v>
+        <v>0.01610663210089297</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.006158465646547511</v>
+        <v>0.02462584224777522</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.002849507336732945</v>
+        <v>-0.06976630717889956</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0154206676998124</v>
+        <v>-0.03780222055626416</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.02321146462036007</v>
+        <v>0.05177900377791288</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
@@ -3033,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.01728249888808908</v>
+        <v>-0.01643358713320188</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.02338622191753119</v>
+        <v>-0.04832559452069823</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.003776899385767069</v>
+        <v>0.002186858880564532</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3054,31 +3054,31 @@
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.008627607961433491</v>
+        <v>-0.05562472772853189</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.01781341073291163</v>
+        <v>0.007646671673143076</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.01302450066862743</v>
+        <v>0.002581573547544026</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,7 +3087,7 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.02314177291470356</v>
+        <v>0.06044467484855377</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02308880068213738</v>
+        <v>-0.05501704182004528</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.002409315848089383</v>
+        <v>0.06440365586856037</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
@@ -3114,34 +3114,34 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.002410014202441448</v>
+        <v>0.002819352952781971</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0009274289311048365</v>
+        <v>-0.07332112335968322</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.01800779164273612</v>
+        <v>0.005694646977547675</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.01347655853922671</v>
+        <v>-0.02597349860032336</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,25 +3150,25 @@
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02800893028649375</v>
+        <v>-0.1205794200017714</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.01100992503657276</v>
+        <v>0.05921964522806786</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.007224075717663542</v>
+        <v>-0.07596194772963713</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
@@ -3177,16 +3177,16 @@
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01475758000551722</v>
+        <v>-0.04943956611969341</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0189503783899173</v>
+        <v>0.0367357044491675</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
@@ -3195,46 +3195,46 @@
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.02490153955404448</v>
+        <v>-0.04331524978973436</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ5" t="n">
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.03201896751237972</v>
+        <v>-0.003939810498593546</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01472592929760382</v>
+        <v>0.02835316433525153</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.00160756235611486</v>
+        <v>0.01926287665029653</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0001925828466532421</v>
+        <v>0.00168137453436129</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.02069341720716554</v>
+        <v>-0.05726199934271723</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
@@ -3246,10 +3246,10 @@
         <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.01307538672866794</v>
+        <v>-0.03987140059240871</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
@@ -3261,10 +3261,10 @@
         <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0003651482801082896</v>
+        <v>0.02393318094859024</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF5" t="n">
         <v>0</v>
@@ -3847,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8188446781826431</v>
+        <v>0.1106605257478138</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1977768885683369</v>
+        <v>-0.04108328449453355</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.03684938307521487</v>
+        <v>-0.01840738978709441</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,22 +3868,22 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.422457980685036</v>
+        <v>0.09773788408402612</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.006366578906329334</v>
+        <v>-0.001910318027405374</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.100532124582405</v>
+        <v>-0.02161433141521221</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3898,79 +3898,79 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2330023137388036</v>
+        <v>0.03226298574612408</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1910953291915937</v>
+        <v>-0.02760022641265806</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.08111370204379585</v>
+        <v>-0.02786599891521438</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.06427397631930656</v>
+        <v>-0.004950334287187013</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.02905675037765349</v>
+        <v>-0.009491911597730513</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.008876358597768044</v>
+        <v>-0.01757975788306368</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.1768957778024401</v>
+        <v>0.07809506100816595</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1409386006529487</v>
+        <v>-0.02486380210852607</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.1121433249931315</v>
+        <v>0.02649218612618839</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
@@ -3982,43 +3982,43 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.279663167106557</v>
+        <v>0.1871275492214928</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.1004057114894126</v>
+        <v>-0.06423778241004235</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.3797164273770242</v>
+        <v>-0.07547277357220804</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
         <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.07135230129856285</v>
+        <v>-0.01172219983968741</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.03717757523109924</v>
+        <v>-0.00846562950326165</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1153450348808757</v>
+        <v>-0.008544987271757089</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,22 +4036,22 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.1967448912271309</v>
+        <v>0.002304469586516034</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.2873850288850401</v>
+        <v>0.01832395760801199</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1142301953402509</v>
+        <v>0.04884618847963722</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,25 +4063,25 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.6549520930296351</v>
+        <v>0.1302212738687747</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.04425305640591849</v>
+        <v>-0.02899974950377515</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.004380479742555023</v>
+        <v>-0.02023118102381103</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -4090,46 +4090,46 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.26839628559662</v>
+        <v>-0.0572660451680114</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.05338124978214504</v>
+        <v>0.04662431915775116</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.08202245875216363</v>
+        <v>0.0077073235960654</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.0304191758224524</v>
+        <v>-0.03165126596225303</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.2903239866763433</v>
+        <v>0.05981022893245355</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.291625696656116</v>
+        <v>0.03840191573570937</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,52 +4138,52 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.2106969486498677</v>
+        <v>-0.06020589954260538</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.1498098551622812</v>
+        <v>0.05304413191514161</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.08166648550794747</v>
+        <v>0.01361917006985035</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.1090452996113983</v>
+        <v>-0.02079117885907035</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.02786010875522124</v>
+        <v>-0.004811940517392787</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01590835313824548</v>
+        <v>-0.006439567585250479</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
@@ -4198,19 +4198,19 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.1376847900153822</v>
+        <v>-0.03780468970755651</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.09331986041033889</v>
+        <v>0.01428001256883357</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.06410177840310215</v>
+        <v>-0.02989745764491979</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4225,22 +4225,22 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.03368169408289465</v>
+        <v>0.009957692461471818</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.09883379532086968</v>
+        <v>0.02805162382793384</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.2048141606502583</v>
+        <v>-0.01163309864740154</v>
       </c>
       <c r="EB7" t="n">
         <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
         <v>0</v>
@@ -4249,52 +4249,52 @@
         <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1195297734637128</v>
+        <v>-0.03547615947645783</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.05772858210338353</v>
+        <v>0.04141946257766672</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.01301415205073796</v>
+        <v>0.006298971679755458</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.2048871664881456</v>
+        <v>-0.03335722014510795</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.1774305837948502</v>
+        <v>-0.03211639790772828</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.189972406510065</v>
+        <v>-0.002656877873373261</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,46 +4306,46 @@
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.2231119931469087</v>
+        <v>-0.0659496869475707</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.09760688117420242</v>
+        <v>0.04903540459816753</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.09855138680183446</v>
+        <v>0.005381444836403034</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.04173065345156896</v>
+        <v>-0.03855158757534916</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.1352257214346882</v>
+        <v>0.01523223752891087</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.06329676444921703</v>
+        <v>0.02068488645329705</v>
       </c>
       <c r="FL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
@@ -4354,28 +4354,28 @@
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.05226116314666736</v>
+        <v>0.001434419265389491</v>
       </c>
       <c r="FR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.191923784848681</v>
+        <v>0.0901094773009016</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.1653297669504655</v>
+        <v>-0.01730965819130865</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
         <v>0</v>
@@ -4384,31 +4384,31 @@
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.1202326839078133</v>
+        <v>-0.04389537671775255</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.0752322826432808</v>
+        <v>0.00823156550767149</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4985,25 +4985,25 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.078440615939895</v>
+        <v>0.1248671664635445</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.007493234767967634</v>
+        <v>0.01271094885080137</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.02181556442242254</v>
+        <v>-0.04010745145788491</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02269957213467511</v>
+        <v>0.1619889580963167</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.02082261074296256</v>
+        <v>-0.01038924452569116</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00573989230799919</v>
+        <v>0.005358425291795898</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-0</v>
@@ -5036,64 +5036,64 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.002852069733786711</v>
+        <v>0.04452569372366458</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.01548030186552145</v>
+        <v>-0.04354286174820867</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01635535939452275</v>
+        <v>0.02788925915763753</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB9" t="n">
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.007126328008862209</v>
+        <v>-0.008730382971707794</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.007375609928480571</v>
+        <v>-0.02232164834127012</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.06279973148163e-05</v>
+        <v>-0.0008519455671913002</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01513482218883552</v>
+        <v>0.07727809779888142</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
@@ -5102,25 +5102,25 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.01952502563204422</v>
+        <v>0.003628003508031285</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.01930571313794038</v>
+        <v>-0.06952632041062128</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.1205892810298722</v>
+        <v>0.2621516155070907</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -5129,10 +5129,10 @@
         <v>-0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.003743826276752533</v>
+        <v>-0.07039292526639433</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.01878238047032248</v>
+        <v>-0.08548481615299341</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -5141,40 +5141,40 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01173778121086731</v>
+        <v>-0.02484376352582409</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF9" t="n">
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.01276169055039268</v>
+        <v>-0.03042969201285126</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.003088622725034245</v>
+        <v>-0.007240556436174</v>
       </c>
       <c r="BI9" t="n">
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.05151131483452023</v>
+        <v>0.006674585115278568</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
@@ -5183,16 +5183,16 @@
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.03462525346208619</v>
+        <v>0.07551979986893194</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0112526194369671</v>
+        <v>0.05372517042843704</v>
       </c>
       <c r="BR9" t="n">
         <v>-0</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT9" t="n">
         <v>0</v>
@@ -5201,25 +5201,25 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.04515211401582013</v>
+        <v>0.164851013005804</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.02372435877672708</v>
+        <v>-0.001531479290388351</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.02944506783506481</v>
+        <v>-0.02627638264700233</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
         <v>-0</v>
@@ -5228,22 +5228,22 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.01089673551085204</v>
+        <v>-0.05283939273680659</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.001677161866602338</v>
+        <v>0.0009167535612477183</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01694329344840169</v>
+        <v>0.03198313754115723</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
@@ -5252,82 +5252,82 @@
         <v>-0</v>
       </c>
       <c r="CM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0111488579736022</v>
+        <v>-0.02856601380916546</v>
       </c>
       <c r="CO9" t="n">
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.01087629149330957</v>
+        <v>0.1092172550548905</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.03937706024176379</v>
+        <v>0.01912189753837016</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.002548794545177541</v>
+        <v>-0.04709114187086791</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0003176679373794217</v>
+        <v>0.002394324092231495</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.02129277914643735</v>
+        <v>0.03778866164862021</v>
       </c>
       <c r="DB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.009810897344161441</v>
+        <v>-0.003065526040565671</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0341812904842009</v>
+        <v>-0.04188441177751473</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.01517675106091414</v>
+        <v>0.07062412372623521</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
         <v>0</v>
@@ -5336,22 +5336,22 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.007500040988034637</v>
+        <v>-0.03298180233961768</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.02463732468573141</v>
+        <v>-0.02650405321252329</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.008143742289483584</v>
+        <v>0.006359355516870027</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5363,103 +5363,103 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.03127676269529355</v>
+        <v>0.01721169774786129</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
         <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.04892820646111953</v>
+        <v>-0.0860065189128079</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0.009052653904648577</v>
+        <v>0.01374662860595434</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0004443121173480709</v>
+        <v>0.009586814066770616</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.008115699980430715</v>
+        <v>-0.02196836419635472</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.002857231194661757</v>
+        <v>-0.01515483119022117</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.002846305331707106</v>
+        <v>-0.008818303713057909</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
         <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.01976737842455332</v>
+        <v>-0.09763670209295496</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0.05929320595179072</v>
+        <v>-0.1225655433484099</v>
       </c>
       <c r="EU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.002927889169117852</v>
+        <v>-0.05522451018044752</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.001230991476891293</v>
+        <v>-0.01004706922425181</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.02141615698589367</v>
+        <v>0.02173089917951222</v>
       </c>
       <c r="FD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
@@ -5471,22 +5471,22 @@
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.02206294913210043</v>
+        <v>-0.05956110471108905</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.04850060544833283</v>
+        <v>0.03795301834982537</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0003694211679771766</v>
+        <v>0.007326419965048406</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
         <v>-0</v>
@@ -5495,40 +5495,40 @@
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.009080936378903268</v>
+        <v>0.01439589194426042</v>
       </c>
       <c r="FR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.01857665728576301</v>
+        <v>0.006576067759583732</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.04035669050242813</v>
+        <v>-0.09402781120137371</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.02789376460830761</v>
+        <v>-0.01419914917717515</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
@@ -5537,13 +5537,13 @@
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.005234109019514656</v>
+        <v>-0.02314344349708755</v>
       </c>
       <c r="GE9" t="n">
         <v>0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2353584272629818</v>
+        <v>0.1702406573772701</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.07280052622804932</v>
+        <v>-0.05421299053780199</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0528452560391639</v>
+        <v>-0.04158649581068084</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5575,22 +5575,22 @@
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1593660384935668</v>
+        <v>0.1579402880315002</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0318171086528885</v>
+        <v>-0.03313904338995323</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.07622730349831229</v>
+        <v>-0.05883006490181579</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5602,85 +5602,85 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0749343815384437</v>
+        <v>0.04902489817261453</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01053245036707389</v>
+        <v>-0.02796802837084134</v>
       </c>
       <c r="W10" t="n">
-        <v>0.04928897431962341</v>
+        <v>-0.0254219214054804</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.02166941891694802</v>
+        <v>-0.007150073157118376</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.0142123054824204</v>
+        <v>-0.01247201625439189</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.002133948069496452</v>
+        <v>-0.02960772508321617</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.02901387018296648</v>
+        <v>0.09037166087752589</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.05547107753771781</v>
+        <v>-0.02218133606242931</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.06551514942092954</v>
+        <v>0.02956471047288188</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,16 +5689,16 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.3684272902578543</v>
+        <v>0.2206951250849493</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.04280775734117782</v>
+        <v>-0.06742391069863134</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1787687601210402</v>
+        <v>-0.1038056558220998</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5707,7 +5707,7 @@
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.01162078512138401</v>
+        <v>-0.01619050542595133</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.01887956494410634</v>
+        <v>-0.00819755619255913</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.07607625040561213</v>
+        <v>-0.02237056622667928</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -5743,22 +5743,22 @@
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.07432122928730399</v>
+        <v>0.007426949731192766</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.06964115532396022</v>
+        <v>0.02430831264294743</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1128007471388463</v>
+        <v>0.05098644307701709</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5770,76 +5770,76 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.174420284486988</v>
+        <v>0.1648152935180472</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0.01399706916102785</v>
+        <v>-0.05911815825689531</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.03838715730894443</v>
+        <v>-0.01852587009419463</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.0680039534130704</v>
+        <v>-0.0670875313863396</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.008654799812302605</v>
+        <v>0.05557075937606124</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.006145154202366211</v>
+        <v>0.009410216732219237</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL10" t="n">
         <v>-0</v>
       </c>
       <c r="CM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.04177488964050055</v>
+        <v>-0.04516218431543135</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.07826790425141808</v>
+        <v>0.06347035049779061</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.1029950553753878</v>
+        <v>0.03979913683687488</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
         <v>-0</v>
@@ -5851,49 +5851,49 @@
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.0422721164558728</v>
+        <v>-0.06892844247018086</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.03299047648153304</v>
+        <v>0.0633462912427952</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.01453156575995737</v>
+        <v>0.01721584114166465</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.02578734647190403</v>
+        <v>-0.0611184240569856</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.0006242239551404605</v>
+        <v>0.05091465522361205</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.01879418614413362</v>
+        <v>-0.02799717105844154</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
@@ -5905,154 +5905,154 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.06112436360902779</v>
+        <v>-0.0364226877256125</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.05466879771177279</v>
+        <v>0.01853286874416477</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.006318745295125026</v>
+        <v>-0.03262382981757132</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.03492782023602484</v>
+        <v>0.02940466376125618</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.04754505466355312</v>
+        <v>0.03341290057438902</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.0280971262866674</v>
+        <v>-0.02852842064649774</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.02718617642908634</v>
+        <v>-0.02736665769379077</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.08981633286381986</v>
+        <v>0.04896314159232908</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.05230341050955174</v>
+        <v>0.005267732759013344</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.07892700724727786</v>
+        <v>-0.04274695143304195</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0.06091665954627435</v>
+        <v>-0.04279442992758988</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01509203844676675</v>
+        <v>-0.01577678722315367</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.05746486315707985</v>
+        <v>-0.07725769190615055</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.02317906368378001</v>
+        <v>0.06065400365272503</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.01521388096963668</v>
+        <v>0.005921448480417293</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.05915613798224972</v>
+        <v>-0.03734210566948622</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.05922847132359615</v>
+        <v>0.02634241036877751</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.02410046570875295</v>
+        <v>0.01411588076934868</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
@@ -6061,61 +6061,61 @@
         <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.01861685089277346</v>
+        <v>0.0008468839301871999</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.01307287904826271</v>
+        <v>0.06914705612776469</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.02221764822499627</v>
+        <v>-0.02470166945726999</v>
       </c>
       <c r="FU10" t="n">
         <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.01709116017962579</v>
+        <v>-0.04373639012212923</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.03266428912953158</v>
+        <v>0.00637699778354964</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6689,46 +6689,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2294415687011784</v>
+        <v>0.05877416640538199</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.01348404093001015</v>
+        <v>-0.009795331700146383</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.04843024479478871</v>
+        <v>-0.02671040282968584</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1214687562888689</v>
+        <v>0.07113363112726362</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.001465634459417278</v>
+        <v>-0.001134726322719764</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.05353523044069109</v>
+        <v>-0.03469688175857666</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6746,19 +6746,19 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.06482211925635069</v>
+        <v>0.01971975729304184</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.01627433679644966</v>
+        <v>-0.009671695508167639</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04356570099205665</v>
+        <v>-0.002711588672419264</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6767,49 +6767,49 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB12" t="n">
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.01304790541115351</v>
+        <v>-0.004443600482395379</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.00252422807446585</v>
+        <v>-0.007079729321282238</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.0006186495810580484</v>
+        <v>-0.01146558129138918</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.005100995323905684</v>
+        <v>0.0400143526481637</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.01497955417291596</v>
+        <v>-0.002605850858254149</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.04440102594272992</v>
+        <v>0.02933880292854502</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6824,46 +6824,46 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.2994513696770269</v>
+        <v>0.09787955828597066</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.02989107216766774</v>
+        <v>-0.007129119792346657</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.06447238222525456</v>
+        <v>-0.04778305449577162</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.02997915686390966</v>
+        <v>-0.02240001188255716</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.02970506482961302</v>
+        <v>-0.0007888943768237654</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.03447659121232267</v>
+        <v>-0.01089176063173139</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,16 +6881,16 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1197973928280732</v>
+        <v>0.02121121979793342</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.01682605263372751</v>
+        <v>0.01787818335066517</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1015899936376978</v>
+        <v>0.03422310243794192</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
@@ -6908,25 +6908,25 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1600409553442957</v>
+        <v>0.08161964309836035</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.02198849378677678</v>
+        <v>-0.03121477992334863</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.01801471830267967</v>
+        <v>-0.009266177545640459</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>-0</v>
@@ -6935,16 +6935,16 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.04967276153207359</v>
+        <v>-0.02148514758768914</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.007143954407006881</v>
+        <v>0.02091638166048588</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.006505641169443219</v>
+        <v>0.017029911238778</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
@@ -6956,28 +6956,28 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.06526533744413744</v>
+        <v>-0.0339646082576685</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.03788765759796864</v>
+        <v>0.01736103048697926</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.08116970938595272</v>
+        <v>0.02948485519325139</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6986,19 +6986,19 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.03268185359346067</v>
+        <v>-0.02275973214322416</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.007164677131447454</v>
+        <v>0.02606363026896259</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.002192838795163054</v>
+        <v>0.01487696677166357</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7013,25 +7013,25 @@
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.01233758113879696</v>
+        <v>0.0008608686192329952</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.03772422098010041</v>
+        <v>0.0053576422093541</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.007995830515257697</v>
+        <v>-0.001608469160617725</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
@@ -7040,49 +7040,49 @@
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.06751620861880829</v>
+        <v>-0.02113479771018487</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.0127785608892525</v>
+        <v>-0.01356269159004158</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.006128372774315907</v>
+        <v>-0.01257932446785177</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.02653513599408256</v>
+        <v>0.03316279436761807</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.01513006306676019</v>
+        <v>0.01311607543051568</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.03833703058492199</v>
+        <v>-0.04858609326312508</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
         <v>0</v>
@@ -7091,22 +7091,22 @@
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.02619968191730065</v>
+        <v>0.008029052839635219</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0.001282537113424753</v>
+        <v>0.01542527347903634</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0306518321179043</v>
+        <v>0.02580585252477851</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
@@ -7115,7 +7115,7 @@
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
@@ -7124,43 +7124,43 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.02303681050191293</v>
+        <v>-0.01276282653822362</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>-0.00246555442918332</v>
+        <v>0.02263356855559358</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.008356528664330476</v>
+        <v>-0.002132911805488612</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>-0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.03305689587434999</v>
+        <v>-0.02467946440398949</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
       </c>
       <c r="FA12" t="n">
-        <v>-0.00105796988179605</v>
+        <v>0.02747947632887314</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.0149013373912724</v>
+        <v>0.01202230136923466</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7175,19 +7175,19 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.03528859900771514</v>
+        <v>0.005770662326229721</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.01744740667862723</v>
+        <v>0.004944386287775192</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.01335501689900912</v>
+        <v>-0.01912728331782124</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7196,31 +7196,31 @@
         <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.0416019188867329</v>
+        <v>0.01107148869741763</v>
       </c>
       <c r="FR12" t="n">
         <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.03076264743596295</v>
+        <v>0.0228393454415434</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.001588381669030447</v>
+        <v>-0.04013107167952896</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
         <v>0</v>
@@ -7232,81 +7232,81 @@
         <v>-0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.004099537797556449</v>
+        <v>0.004328334163746257</v>
       </c>
       <c r="GA12" t="n">
         <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.0304280262451644</v>
+        <v>-0.004536464848833277</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
         <v>0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2700343867787434</v>
+        <v>0.04225856880723029</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00322742144273648</v>
+        <v>-0.02974543542849333</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1546901231215702</v>
+        <v>-0.03175554471311715</v>
       </c>
       <c r="G13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1940086088304648</v>
+        <v>0.0823125583627017</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.006191633026538121</v>
+        <v>-0.0483319630854372</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1238869806179642</v>
+        <v>-0.03252730785808778</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,46 +7315,46 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0216924044147888</v>
+        <v>0.04130977792607964</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.03140394153028445</v>
+        <v>-0.01823303808486686</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.01987292371825753</v>
+        <v>-0.00311263170534497</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.01704544419653729</v>
+        <v>-0.006304016023763506</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.008542956962004003</v>
+        <v>-0.01823619493132902</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.003055013525963564</v>
+        <v>0.001219673280595191</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,67 +7363,67 @@
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0256246775258343</v>
+        <v>0.01852307297722506</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.03333486875614245</v>
+        <v>0.01102702346618838</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.07331319517702112</v>
+        <v>-0.01807778265127776</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT13" t="n">
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.2411897915746122</v>
+        <v>0.1175000951819072</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.02400532754532168</v>
+        <v>-0.0557928963280621</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.1129666598919063</v>
+        <v>-0.06249418118264452</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0730357806877743</v>
+        <v>-0.0248532037784459</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,64 +7432,64 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.02176753328465161</v>
+        <v>-0.03086224824018117</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.03810291797696697</v>
+        <v>0.002682655783442027</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>-0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.09066402271859893</v>
+        <v>0.03331496862377559</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.05032110442800378</v>
+        <v>0.04085430252633224</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01299037422086237</v>
+        <v>0.004154229204979497</v>
       </c>
       <c r="BR13" t="n">
         <v>-0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.1147509525048969</v>
+        <v>0.1001662797267008</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.02589974529496144</v>
+        <v>-0.01729673392972596</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.03169220924971227</v>
+        <v>-0.01750530196464756</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7498,25 +7498,25 @@
         <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD13" t="n">
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.06081893203149629</v>
+        <v>-0.01832503592800697</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.01354139852552244</v>
+        <v>0.02642010532276049</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.04635236829000789</v>
+        <v>0.01892744218190388</v>
       </c>
       <c r="CJ13" t="n">
         <v>-0</v>
@@ -7525,58 +7525,58 @@
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.03475910697238</v>
+        <v>-0.05472628693775065</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.02431735376124465</v>
+        <v>0.07791089998968746</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.04932204451737761</v>
+        <v>0.01690557684594217</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
         <v>0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.04264945623710398</v>
+        <v>-0.0120412058843007</v>
       </c>
       <c r="CX13" t="n">
         <v>-0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.01282408076205545</v>
+        <v>0.02474270827901071</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.04531709364515944</v>
+        <v>0.02097242005317063</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
       </c>
       <c r="DC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="n">
         <v>0</v>
@@ -7585,61 +7585,61 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.009944807319549408</v>
+        <v>0.006144187582120127</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.00192826074886549</v>
+        <v>-0.007231002986614104</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.001715813051056891</v>
+        <v>0.002965251387515097</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
         <v>-0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.03396835094888168</v>
+        <v>-0.02294092055341535</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01366434109208885</v>
+        <v>0.01552761267876717</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.01659495410422092</v>
+        <v>-0.005597417060257313</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU13" t="n">
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.002974883652458544</v>
+        <v>0.02575793684722476</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
@@ -7648,10 +7648,10 @@
         <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.03468804707754825</v>
+        <v>-0.04476814204717315</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.006940424379221811</v>
+        <v>-0.01856038098765056</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
@@ -7660,13 +7660,13 @@
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
         <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.03296306157904068</v>
+        <v>0.03042981230409111</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,52 +7675,52 @@
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.01671389283280133</v>
+        <v>0.01099472643280115</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.03166213758333809</v>
+        <v>0.009593827825097372</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.0392548360869872</v>
+        <v>-0.003271266549640844</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.03010981300395878</v>
+        <v>-0.02356176935478456</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.07273602257293967</v>
+        <v>0.01870255111777034</v>
       </c>
       <c r="EU13" t="n">
         <v>-0</v>
       </c>
       <c r="EV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.04532195418652545</v>
+        <v>-0.01868885709800841</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
@@ -7729,79 +7729,79 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.006300509490901532</v>
+        <v>0.01964845384717541</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.04855625296586386</v>
+        <v>0.0173460902329979</v>
       </c>
       <c r="FD13" t="n">
         <v>-0</v>
       </c>
       <c r="FE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.008908109390083028</v>
+        <v>-0.01019604737014612</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.03219622944241578</v>
+        <v>0.01090346056357341</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.02968749425003416</v>
+        <v>0.01052414277189296</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.0120324471440401</v>
+        <v>0.009010518935499482</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.03535363353311649</v>
+        <v>-0.04906042433243893</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.002451591828547806</v>
+        <v>0.0006342167723409624</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
         <v>-0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.02211526536235643</v>
+        <v>0.0001597347646472745</v>
       </c>
       <c r="GA13" t="n">
         <v>-0</v>
@@ -7813,7 +7813,7 @@
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.04273523048035299</v>
+        <v>-0.001352596343011439</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7822,7 +7822,7 @@
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7833,22 +7833,22 @@
         <v>-0</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.08647759691063145</v>
+        <v>-0.04292543580569948</v>
       </c>
       <c r="D14" t="n">
-        <v>0.191252293527379</v>
+        <v>-0.008311545848139215</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.06067994288443658</v>
+        <v>-0.06355678742131506</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
         <v>-0</v>
@@ -7857,43 +7857,43 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.09408195442377786</v>
+        <v>-0.04145299697809569</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2151549885615014</v>
+        <v>-0.02607383557244886</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0362756764209044</v>
+        <v>-0.05733647045720108</v>
       </c>
       <c r="O14" t="n">
         <v>-0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R14" t="n">
         <v>-0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.02636239044876619</v>
+        <v>-0.01119361227577141</v>
       </c>
       <c r="V14" t="n">
-        <v>0.06254021036834743</v>
+        <v>0.03262109145172526</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01059689568770289</v>
+        <v>0.00455236299757369</v>
       </c>
       <c r="X14" t="n">
         <v>-0</v>
@@ -7905,7 +7905,7 @@
         <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -7914,13 +7914,13 @@
         <v>-0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.00609624349755699</v>
+        <v>-0.0153747436136917</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.01566280527240501</v>
+        <v>-0.02145555551000524</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.01318733007039028</v>
+        <v>-0.01423588188736574</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
@@ -7935,46 +7935,46 @@
         <v>-0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.001643436910129717</v>
+        <v>-0.04784408309568089</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.03642279338592527</v>
+        <v>0.02512972907250665</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.04475960449407976</v>
+        <v>0.006408359407473751</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.0867373275139554</v>
+        <v>-0.05191700111631026</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.1467504208074926</v>
+        <v>0.1054484865342001</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.1705370545009862</v>
+        <v>-0.09846282986565827</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -7995,13 +7995,13 @@
         <v>-0</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.02111361674014537</v>
+        <v>-0.007699918299909268</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.02503961651707857</v>
+        <v>-0.09745276797531563</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.02799769100760607</v>
+        <v>-0.03939587002374281</v>
       </c>
       <c r="BH14" t="n">
         <v>-0</v>
@@ -8010,25 +8010,25 @@
         <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>-0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.04154813699904164</v>
+        <v>0.03653474752149709</v>
       </c>
       <c r="BO14" t="n">
-        <v>-0.01784053240639226</v>
+        <v>0.05526940393871166</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.1343780904482073</v>
+        <v>0.08535451587886385</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
@@ -8037,82 +8037,82 @@
         <v>-0</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW14" t="n">
-        <v>-0.08958982640584466</v>
+        <v>-0.05227695066225822</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.09244012203789666</v>
+        <v>0.1061584852834158</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.09952979094391484</v>
+        <v>-0.01550759666209553</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE14" t="n">
         <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.05168399101716321</v>
+        <v>0.04270204722156511</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.04179652545717805</v>
+        <v>0.020497162111676</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.01261111360210255</v>
+        <v>0.01076020243683215</v>
       </c>
       <c r="CI14" t="n">
         <v>-0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
         <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.01664612659487904</v>
+        <v>0.01478062724193715</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.03816506490799307</v>
+        <v>0.03576996478478125</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0916985195278576</v>
+        <v>0.05431346345035965</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
         <v>-0</v>
@@ -8121,52 +8121,52 @@
         <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
         <v>-0</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.03333888209838561</v>
+        <v>0.0312465356799401</v>
       </c>
       <c r="CY14" t="n">
-        <v>-0.03555293617812889</v>
+        <v>0.01995211302569123</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.01775658320545278</v>
+        <v>0.02291807613973434</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
         <v>-0</v>
       </c>
       <c r="DE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.0005014144055817796</v>
+        <v>0.01891177583558858</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.03330228328136463</v>
+        <v>-0.01021705853476427</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.001050469570105358</v>
+        <v>0.0006730315187227773</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
@@ -8175,49 +8175,49 @@
         <v>-0</v>
       </c>
       <c r="DM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO14" t="n">
         <v>0</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.04735769477368136</v>
+        <v>0.00275947612103228</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0.009862500362254221</v>
+        <v>-0.00876987907459973</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.04478355704944786</v>
+        <v>0.04673349839998247</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.005607314039063905</v>
+        <v>-0.03324291125852837</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.0191746052753653</v>
+        <v>-0.02821403880222457</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0315182822787949</v>
+        <v>-0.04444435256022671</v>
       </c>
       <c r="EB14" t="n">
         <v>-0</v>
@@ -8235,22 +8235,22 @@
         <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.05715343788705531</v>
+        <v>0.003802103436820325</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0.06272202117677504</v>
+        <v>0.03436894061076303</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.01509533535791242</v>
+        <v>-0.002163534575557847</v>
       </c>
       <c r="EK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM14" t="n">
         <v>0</v>
@@ -8259,139 +8259,139 @@
         <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.02906799420233681</v>
+        <v>0.0005590405284794529</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0.02985297105267653</v>
+        <v>0.004747107614538873</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.02094970094072121</v>
+        <v>0.01510731242425857</v>
       </c>
       <c r="ET14" t="n">
         <v>-0</v>
       </c>
       <c r="EU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY14" t="n">
         <v>0</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.04219433364021585</v>
+        <v>0.03306365111530757</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.03810921106738524</v>
+        <v>0.008310726948759905</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.020056212085409</v>
+        <v>0.01410238303262746</v>
       </c>
       <c r="FC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE14" t="n">
         <v>-0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
         <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.008954098733024239</v>
+        <v>0.05126707458397112</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.03623377136693363</v>
+        <v>-0.013820468802514</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.03786126679740491</v>
+        <v>-0.06684801662456701</v>
       </c>
       <c r="FL14" t="n">
         <v>0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
         <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.01079938055494685</v>
+        <v>-0.002389535344959889</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.003386454281482734</v>
+        <v>0.004952868102828394</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.003952767087650896</v>
+        <v>0.05104289662592847</v>
       </c>
       <c r="FU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV14" t="n">
         <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
         <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.03477554824109785</v>
+        <v>0.01737158806162473</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.0322330896641382</v>
+        <v>-0.02277762817849984</v>
       </c>
       <c r="GC14" t="n">
         <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -8965,25 +8965,25 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.2697112663162954</v>
+        <v>0.2162887477656024</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2557671359851261</v>
+        <v>-0.05228066419874362</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.07128680755480456</v>
+        <v>-0.08198088221356714</v>
       </c>
       <c r="G16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>-0</v>
@@ -8995,7 +8995,7 @@
         <v>-0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1896010312799872</v>
+        <v>0.3349952786624076</v>
       </c>
       <c r="L16" t="n">
         <v>-0</v>
@@ -9004,13 +9004,13 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2438727739934629</v>
+        <v>-0.1178206046150323</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.07896751940191535</v>
+        <v>-0.0910986587373158</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -9019,10 +9019,10 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.06322352311322645</v>
+        <v>0.07681951081217332</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
@@ -9031,25 +9031,25 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.02569413257929242</v>
+        <v>-0.06657455693732676</v>
       </c>
       <c r="X16" t="n">
-        <v>0.05799320869457764</v>
+        <v>0.008368033767510576</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB16" t="n">
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.03306028924166482</v>
+        <v>-0.01859010226187395</v>
       </c>
       <c r="AD16" t="n">
         <v>-0</v>
@@ -9058,10 +9058,10 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.003828476504221393</v>
+        <v>-0.07262378725970728</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.01060300473128163</v>
+        <v>0.01954372620893506</v>
       </c>
       <c r="AH16" t="n">
         <v>-0</v>
@@ -9070,139 +9070,139 @@
         <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.08124858888373294</v>
+        <v>0.01087558902982193</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.02525126080807432</v>
+        <v>-0.09528989601878179</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.0330108357937478</v>
+        <v>-0.03156174931290796</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT16" t="n">
         <v>-0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.2692884931163552</v>
+        <v>0.3994757843658667</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.1249294755616418</v>
+        <v>-0.169567182085729</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.0582202736046037</v>
+        <v>-0.1131324932757719</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
       </c>
       <c r="BC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.05624525010255706</v>
+        <v>-0.07042018863133448</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1375711230735568</v>
+        <v>-0.02659189738593197</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.02024607875998934</v>
+        <v>0.01380705031435752</v>
       </c>
       <c r="BI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.1148288699831795</v>
+        <v>0.1328394421046901</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
         <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.04014841464887148</v>
+        <v>0.1233418273527216</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.06066083948006174</v>
+        <v>0.05727626671256395</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.1635869482478081</v>
+        <v>0.2308538063487962</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.06075972693405063</v>
+        <v>-0.06291131376812045</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.03145173185389488</v>
+        <v>-0.02725785763236487</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
         <v>-0</v>
@@ -9211,7 +9211,7 @@
         <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.0409194548698688</v>
+        <v>-0.07049999076729432</v>
       </c>
       <c r="CF16" t="n">
         <v>-0</v>
@@ -9220,25 +9220,25 @@
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.04369827590317353</v>
+        <v>0.04682277897444904</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.02894693351563159</v>
+        <v>0.03320501668023248</v>
       </c>
       <c r="CJ16" t="n">
         <v>-0</v>
       </c>
       <c r="CK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.03823300779295159</v>
+        <v>-0.1739178363720466</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
@@ -9247,37 +9247,37 @@
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.004179822180602155</v>
+        <v>0.1158875340830315</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.01759141407494051</v>
+        <v>-0.002714365100835953</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV16" t="n">
         <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.02006054995598947</v>
+        <v>-0.0646223607155522</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.04091514675381996</v>
+        <v>0.0197479312787979</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.03863611397713657</v>
+        <v>0.04071492472105324</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
@@ -9292,19 +9292,19 @@
         <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.04962236294407174</v>
+        <v>-0.06064517664664965</v>
       </c>
       <c r="DG16" t="n">
         <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.02933143719296313</v>
+        <v>-0.03460384521393041</v>
       </c>
       <c r="DJ16" t="n">
-        <v>-0.005401130714929194</v>
+        <v>-0.02907929075517311</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
@@ -9313,25 +9313,25 @@
         <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.03705179235902959</v>
+        <v>-0.0250796505869166</v>
       </c>
       <c r="DP16" t="n">
         <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.01980312841182075</v>
+        <v>-0.001322809644686774</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.0846217242470344</v>
+        <v>-0.05099876687509348</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
@@ -9343,49 +9343,49 @@
         <v>-0</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.01155286704594499</v>
+        <v>0.0572412741349351</v>
       </c>
       <c r="DY16" t="n">
         <v>0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.06862192709005172</v>
+        <v>-0.04978097950706631</v>
       </c>
       <c r="EB16" t="n">
-        <v>-0.05770087725230413</v>
+        <v>-0.0126430627169464</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE16" t="n">
         <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.01740851413798805</v>
+        <v>-0.004174256368875164</v>
       </c>
       <c r="EH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.0425632461147375</v>
+        <v>-0.01446529451323079</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.008000634138381261</v>
+        <v>0.03391995267022513</v>
       </c>
       <c r="EL16" t="n">
         <v>-0</v>
@@ -9394,28 +9394,28 @@
         <v>-0</v>
       </c>
       <c r="EN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.03951865638767837</v>
+        <v>0.01505116928709929</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.01377292655453901</v>
+        <v>-0.0689572341737112</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.05951782746505498</v>
+        <v>0.002970958738938114</v>
       </c>
       <c r="EU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
@@ -9424,37 +9424,37 @@
         <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.01400750451449283</v>
+        <v>-0.08089954691669182</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.03638230997149372</v>
+        <v>0.02529299084784481</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.04256793180166351</v>
+        <v>0.02278939522340722</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF16" t="n">
         <v>-0</v>
       </c>
       <c r="FG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.0519756023612194</v>
+        <v>-0.06433741944868643</v>
       </c>
       <c r="FI16" t="n">
         <v>-0</v>
@@ -9463,16 +9463,16 @@
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.0398169324650211</v>
+        <v>0.1027123741693048</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.02360848956523366</v>
+        <v>0.007383766775977008</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
@@ -9481,7 +9481,7 @@
         <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.007060472833071993</v>
+        <v>0.008375698194350682</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
@@ -9490,46 +9490,46 @@
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.006738741077010247</v>
+        <v>-0.02522238446388338</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.0005144385711839201</v>
+        <v>-0.01933869774518156</v>
       </c>
       <c r="FV16" t="n">
         <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.03867406644903205</v>
+        <v>-0.09055431901407984</v>
       </c>
       <c r="GA16" t="n">
         <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.05184840752571772</v>
+        <v>0.04837273417834912</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="17">
@@ -9537,19 +9537,19 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4580576506375309</v>
+        <v>0.3583315913218956</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.205351095239862</v>
+        <v>-0.184007061372519</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.145056054760145</v>
+        <v>-0.02966955782605313</v>
       </c>
       <c r="F17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>-0</v>
@@ -9564,16 +9564,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3814656438684291</v>
+        <v>0.3912440335236052</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2326106099819016</v>
+        <v>-0.2265473314141546</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2007577219096115</v>
+        <v>-0.05459282795764821</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9582,28 +9582,28 @@
         <v>-0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1290427741981881</v>
+        <v>0.09228495514927243</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.02122955699306828</v>
+        <v>-0.04945717862579346</v>
       </c>
       <c r="W17" t="n">
-        <v>0.112728021777426</v>
+        <v>-0.07377798274748838</v>
       </c>
       <c r="X17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
@@ -9615,52 +9615,52 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1164044171404286</v>
+        <v>-0.05288855718698368</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.001051074903932042</v>
+        <v>-0.06121967710739082</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.008555419269692922</v>
+        <v>-0.06311031412669739</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.04959428377689469</v>
+        <v>0.1363129420980341</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.02773418451528067</v>
+        <v>-0.08707806272189711</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.04358339021983011</v>
+        <v>0.04659968913448468</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
@@ -9669,28 +9669,28 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.427311033972497</v>
+        <v>0.3304449921377042</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.01915956983420828</v>
+        <v>-0.09335352562727282</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.1119733229876162</v>
+        <v>-0.1157598625588407</v>
       </c>
       <c r="AY17" t="n">
         <v>-0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
         <v>-0</v>
@@ -9699,16 +9699,16 @@
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.04316589169369832</v>
+        <v>-0.02126321579149268</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.09480830400076243</v>
+        <v>-0.04844765425207694</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.2146313005815216</v>
+        <v>-0.0500498756812943</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
@@ -9717,7 +9717,7 @@
         <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
@@ -9726,25 +9726,25 @@
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.08703996130856226</v>
+        <v>-0.02258798776008116</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.03683317098437166</v>
+        <v>0.003658909098111481</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.08321253298826718</v>
+        <v>0.06750467270497701</v>
       </c>
       <c r="BQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT17" t="n">
         <v>-0</v>
@@ -9753,22 +9753,22 @@
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.2277852692053173</v>
+        <v>0.2628865716780778</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
-        <v>-0.01574537804828058</v>
+        <v>-0.1252956690770637</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.08735844688742933</v>
+        <v>-0.04365532647390668</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB17" t="n">
         <v>0</v>
@@ -9780,22 +9780,22 @@
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.09805924910137051</v>
+        <v>-0.1118252911580354</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.01892124522967754</v>
+        <v>0.1008909586308307</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.004202849956216864</v>
+        <v>0.007441291125440556</v>
       </c>
       <c r="CI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
@@ -9807,19 +9807,19 @@
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.07837019424394656</v>
+        <v>-0.1453089733413717</v>
       </c>
       <c r="CO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0.09180424134498538</v>
+        <v>0.2005301717426625</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.1181239892814337</v>
+        <v>0.09734690384528293</v>
       </c>
       <c r="CR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS17" t="n">
         <v>-0</v>
@@ -9834,22 +9834,22 @@
         <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.07526735189037474</v>
+        <v>-0.1011708193103983</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.0303300209134582</v>
+        <v>0.1069778178875152</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.002348790323582044</v>
+        <v>0.009708097232004291</v>
       </c>
       <c r="DA17" t="n">
         <v>-0</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
         <v>-0</v>
@@ -9861,22 +9861,22 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.04333994723118254</v>
+        <v>-0.1039744312454602</v>
       </c>
       <c r="DG17" t="n">
         <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.01599704792258639</v>
+        <v>0.01694539381727014</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.01166868159854023</v>
+        <v>-0.04785192282216691</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL17" t="n">
         <v>0</v>
@@ -9888,22 +9888,22 @@
         <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.04119019030273775</v>
+        <v>-0.05645628902080266</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0.04197880003801555</v>
+        <v>0.062934534871527</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.06227667457106512</v>
+        <v>-0.006217208729557742</v>
       </c>
       <c r="DS17" t="n">
         <v>-0</v>
       </c>
       <c r="DT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU17" t="n">
         <v>-0</v>
@@ -9912,25 +9912,25 @@
         <v>0</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.04696700695163541</v>
+        <v>0.04636585346232369</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0.02306854620718968</v>
+        <v>-0.04879079529207104</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.01628558703276568</v>
+        <v>0.03148017316517618</v>
       </c>
       <c r="EB17" t="n">
         <v>0</v>
       </c>
       <c r="EC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED17" t="n">
         <v>0</v>
@@ -9939,52 +9939,52 @@
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.05397055325512113</v>
+        <v>-0.0772598853809779</v>
       </c>
       <c r="EH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.04985963904106451</v>
+        <v>0.05098951393091653</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.07187535903197635</v>
+        <v>0.03864027020576199</v>
       </c>
       <c r="EK17" t="n">
         <v>-0</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
         <v>-0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.08785779522901122</v>
+        <v>-0.03765442311197276</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.006182865272743335</v>
+        <v>0.04900518543583689</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.06674715185584068</v>
+        <v>-0.03029906768661464</v>
       </c>
       <c r="ET17" t="n">
         <v>-0</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
@@ -9993,25 +9993,25 @@
         <v>-0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.08447650327114783</v>
+        <v>-0.1236318686981556</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.03933890995438718</v>
+        <v>0.1082278799899951</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.005923621861350622</v>
+        <v>0.0007432476642976097</v>
       </c>
       <c r="FC17" t="n">
         <v>-0</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>0</v>
@@ -10023,19 +10023,19 @@
         <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.01036309681897543</v>
+        <v>-0.08568005698687031</v>
       </c>
       <c r="FI17" t="n">
         <v>-0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.07460920971420573</v>
+        <v>0.07966160177647102</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.06694966287127836</v>
+        <v>0.02579023594220107</v>
       </c>
       <c r="FL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
@@ -10044,61 +10044,61 @@
         <v>0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
         <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.003096628198665665</v>
+        <v>0.002804675183175267</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.03377052463789688</v>
+        <v>0.04783433431799754</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.01132049263542181</v>
+        <v>-0.0159574490494727</v>
       </c>
       <c r="FU17" t="n">
         <v>-0</v>
       </c>
       <c r="FV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.02704514575672932</v>
+        <v>-0.1162232426299883</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0.07265413171494416</v>
+        <v>0.03051687469418154</v>
       </c>
       <c r="GC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -10106,22 +10106,22 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1723987628840414</v>
+        <v>0.2781208396040979</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.02878120798766848</v>
+        <v>0.009189771772644566</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1056631885175192</v>
+        <v>-0.1059620839455313</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H18" t="n">
         <v>-0</v>
@@ -10133,73 +10133,73 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1303372553484457</v>
+        <v>0.4054600378008912</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.03139544906742783</v>
+        <v>-0.04837016181845003</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1245660637998195</v>
+        <v>-0.1076279086185027</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.02829208068875351</v>
+        <v>0.0828203926869872</v>
       </c>
       <c r="U18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.002812711944421419</v>
+        <v>-0.03957846104456834</v>
       </c>
       <c r="X18" t="n">
-        <v>0.009844042858367895</v>
+        <v>-0.001461474316510767</v>
       </c>
       <c r="Y18" t="n">
         <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB18" t="n">
         <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.02476687481329457</v>
+        <v>-0.005034604095979153</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.01881275443925404</v>
+        <v>-0.1292160597197905</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.0016514952382638</v>
+        <v>-0.04013570807912059</v>
       </c>
       <c r="AH18" t="n">
         <v>-0</v>
@@ -10208,28 +10208,28 @@
         <v>-0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.01484964952480969</v>
+        <v>0.0411092023533059</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.02134963648211018</v>
+        <v>-0.01557661999143325</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.02334797556906985</v>
+        <v>-0.0264181252697086</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
@@ -10238,28 +10238,28 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.1225107918069968</v>
+        <v>0.288388604315063</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
       </c>
       <c r="AW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.01958673837847706</v>
+        <v>-0.1303937720258318</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.04641947139585179</v>
+        <v>-0.0522819954862488</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
         <v>0</v>
@@ -10268,34 +10268,34 @@
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.04647155343606672</v>
+        <v>0.02924828221279987</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.03908003452301941</v>
+        <v>-0.04728454596811379</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.04382606902363451</v>
+        <v>-0.05610193869740143</v>
       </c>
       <c r="BI18" t="n">
         <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.05351040737866983</v>
+        <v>0.03513320213858578</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
@@ -10304,25 +10304,25 @@
         <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.03078247026571133</v>
+        <v>0.04637930923324914</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.01030996146448249</v>
+        <v>-0.006703235771041289</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
         <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.05519815705707916</v>
+        <v>0.2171830898741407</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
@@ -10331,10 +10331,10 @@
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.001632628504062605</v>
+        <v>-0.01995444849791713</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0.02208986197621645</v>
+        <v>-0.03263829869814683</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
@@ -10349,7 +10349,7 @@
         <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.03137436485175196</v>
+        <v>-0.08227835840469387</v>
       </c>
       <c r="CF18" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.003541657467835877</v>
+        <v>0.01602087030477683</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.02868517082576157</v>
+        <v>0.04469077563509167</v>
       </c>
       <c r="CJ18" t="n">
         <v>0</v>
@@ -10370,40 +10370,40 @@
         <v>0</v>
       </c>
       <c r="CL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM18" t="n">
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.02048968238872666</v>
+        <v>-0.1814629736591558</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.002366345556868584</v>
+        <v>0.1192558523616098</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.01417210151994259</v>
+        <v>0.04336776205260882</v>
       </c>
       <c r="CS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT18" t="n">
         <v>-0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.02229133703981448</v>
+        <v>-0.08529314147252146</v>
       </c>
       <c r="CX18" t="n">
         <v>-0</v>
@@ -10412,13 +10412,13 @@
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.003427655245301019</v>
+        <v>-0.002661136709259138</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.02906590575492075</v>
+        <v>0.05135121374150443</v>
       </c>
       <c r="DB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC18" t="n">
         <v>-0</v>
@@ -10427,22 +10427,22 @@
         <v>0</v>
       </c>
       <c r="DE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.02855463953770123</v>
+        <v>-0.04964997637649543</v>
       </c>
       <c r="DG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.01108635831631471</v>
+        <v>-0.1174610057643515</v>
       </c>
       <c r="DJ18" t="n">
-        <v>-0.0004950602741731801</v>
+        <v>-0.0001773083222894949</v>
       </c>
       <c r="DK18" t="n">
         <v>0</v>
@@ -10451,52 +10451,52 @@
         <v>-0</v>
       </c>
       <c r="DM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.01852472113655756</v>
+        <v>-0.08208077160071844</v>
       </c>
       <c r="DP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.01181293034050437</v>
+        <v>0.06129647753597657</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.00861986482178057</v>
+        <v>-0.02564224142130199</v>
       </c>
       <c r="DT18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW18" t="n">
         <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.01845244840384014</v>
+        <v>-0.007663064275406998</v>
       </c>
       <c r="DY18" t="n">
         <v>0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA18" t="n">
-        <v>-0.01107593024603022</v>
+        <v>0.09752091966627344</v>
       </c>
       <c r="EB18" t="n">
-        <v>-0.02284091986929819</v>
+        <v>-0.05614531058945501</v>
       </c>
       <c r="EC18" t="n">
         <v>-0</v>
@@ -10508,10 +10508,10 @@
         <v>-0</v>
       </c>
       <c r="EF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.01503187959446533</v>
+        <v>-0.005447145102909749</v>
       </c>
       <c r="EH18" t="n">
         <v>-0</v>
@@ -10520,13 +10520,13 @@
         <v>0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.001805457809189229</v>
+        <v>-0.02389650632500838</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.01750024886310283</v>
+        <v>0.0211441092651629</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
         <v>-0</v>
@@ -10535,22 +10535,22 @@
         <v>-0</v>
       </c>
       <c r="EO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.007782632256944743</v>
+        <v>0.007012822393447507</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>-0.001379850397226107</v>
+        <v>-0.08594872617132573</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.009532205344500191</v>
+        <v>0.06453404177035121</v>
       </c>
       <c r="EU18" t="n">
         <v>-0</v>
@@ -10559,40 +10559,40 @@
         <v>0</v>
       </c>
       <c r="EW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX18" t="n">
         <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.02237336950222592</v>
+        <v>-0.09618832026171878</v>
       </c>
       <c r="EZ18" t="n">
         <v>0</v>
       </c>
       <c r="FA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>-0.00255670512724954</v>
+        <v>-0.008714438622305667</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.03126891122922373</v>
+        <v>0.04358745929419958</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>0</v>
       </c>
       <c r="FF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG18" t="n">
         <v>0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.00375374065088266</v>
+        <v>-0.1381607477981377</v>
       </c>
       <c r="FI18" t="n">
         <v>-0</v>
@@ -10601,37 +10601,37 @@
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>-0.02620251837544547</v>
+        <v>0.1011075224075725</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.02443331126529425</v>
+        <v>0.04354282919933999</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP18" t="n">
         <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>9.872784703997422e-05</v>
+        <v>0.0009143979824285679</v>
       </c>
       <c r="FR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS18" t="n">
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.001862402504787877</v>
+        <v>-0.006406294649680885</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.02242977868505019</v>
+        <v>-0.06315630925958041</v>
       </c>
       <c r="FV18" t="n">
         <v>-0</v>
@@ -10640,25 +10640,25 @@
         <v>-0</v>
       </c>
       <c r="FX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>-0.01419852744052202</v>
+        <v>-0.003772904515519898</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
         <v>-0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.02293758314463275</v>
+        <v>-0.001176845875757272</v>
       </c>
       <c r="GE18" t="n">
         <v>-0</v>
@@ -10667,7 +10667,7 @@
         <v>-0</v>
       </c>
       <c r="GG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -10675,16 +10675,16 @@
         <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>0.7819810661933297</v>
+        <v>0.6662571941207194</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3384013531338657</v>
+        <v>-0.2863168604383984</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2539926269930842</v>
+        <v>-0.135717015841575</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -10702,16 +10702,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5558554532105916</v>
+        <v>0.7119901144004289</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.301285318496822</v>
+        <v>-0.397268335190297</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2652576094905764</v>
+        <v>-0.2628946330462514</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -10729,70 +10729,70 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.165873255803108</v>
+        <v>0.08886814472189229</v>
       </c>
       <c r="U19" t="n">
         <v>-0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0523974134044383</v>
+        <v>-0.1063519284128641</v>
       </c>
       <c r="W19" t="n">
-        <v>0.05809496335394593</v>
+        <v>-0.1308827124040379</v>
       </c>
       <c r="X19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>-0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1153947708793448</v>
+        <v>-9.563372607180644e-05</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.006531690187587138</v>
+        <v>-0.1392701299213998</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.009900240398767019</v>
+        <v>-0.1229464418892886</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.04904525539829507</v>
+        <v>0.2267021658968792</v>
       </c>
       <c r="AM19" t="n">
         <v>-0</v>
       </c>
       <c r="AN19" t="n">
-        <v>-0.05633975692182677</v>
+        <v>-0.1207720277848394</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.09210187950550913</v>
+        <v>0.07290914600787163</v>
       </c>
       <c r="AP19" t="n">
         <v>0</v>
@@ -10807,28 +10807,28 @@
         <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.574212899513159</v>
+        <v>0.6012195907162976</v>
       </c>
       <c r="AV19" t="n">
         <v>-0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.03552530412749356</v>
+        <v>-0.1315517789647744</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.02867291963970262</v>
+        <v>-0.2948007913621193</v>
       </c>
       <c r="AY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
         <v>-0</v>
@@ -10837,16 +10837,16 @@
         <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.06941818720214796</v>
+        <v>-0.0405042707656202</v>
       </c>
       <c r="BE19" t="n">
         <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>-0.1629785606274899</v>
+        <v>-0.07586754044249902</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.2953253412387802</v>
+        <v>-0.03198515889515898</v>
       </c>
       <c r="BH19" t="n">
         <v>0</v>
@@ -10855,7 +10855,7 @@
         <v>-0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK19" t="n">
         <v>0</v>
@@ -10864,22 +10864,22 @@
         <v>-0</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.1729802192208827</v>
+        <v>0.01025442715896322</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.04022378588402906</v>
+        <v>0.02469442789164763</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.150270962294255</v>
+        <v>0.1189465379441768</v>
       </c>
       <c r="BQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS19" t="n">
         <v>-0</v>
@@ -10888,28 +10888,28 @@
         <v>-0</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.2818466652231957</v>
+        <v>0.4052459572621319</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX19" t="n">
-        <v>0.02686385090971881</v>
+        <v>-0.1888898337790406</v>
       </c>
       <c r="BY19" t="n">
-        <v>0.03863339641600002</v>
+        <v>-0.1266341351074275</v>
       </c>
       <c r="BZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA19" t="n">
         <v>-0</v>
       </c>
       <c r="CB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC19" t="n">
         <v>0</v>
@@ -10918,16 +10918,16 @@
         <v>-0</v>
       </c>
       <c r="CE19" t="n">
-        <v>-0.138382533181111</v>
+        <v>-0.2045987728131982</v>
       </c>
       <c r="CF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG19" t="n">
-        <v>0.03431227045874673</v>
+        <v>0.1253708540052066</v>
       </c>
       <c r="CH19" t="n">
-        <v>-0.009454442174908099</v>
+        <v>0.04972275656142233</v>
       </c>
       <c r="CI19" t="n">
         <v>-0</v>
@@ -10939,25 +10939,25 @@
         <v>0</v>
       </c>
       <c r="CL19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM19" t="n">
         <v>0</v>
       </c>
       <c r="CN19" t="n">
-        <v>-0.03652124444163558</v>
+        <v>-0.2685781069313327</v>
       </c>
       <c r="CO19" t="n">
         <v>-0</v>
       </c>
       <c r="CP19" t="n">
-        <v>-0.1527370294687676</v>
+        <v>0.293697310418195</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-0.1084415628809155</v>
+        <v>0.1353662201809905</v>
       </c>
       <c r="CR19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS19" t="n">
         <v>-0</v>
@@ -10966,22 +10966,22 @@
         <v>-0</v>
       </c>
       <c r="CU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV19" t="n">
         <v>0</v>
       </c>
       <c r="CW19" t="n">
-        <v>-0.1057229281763236</v>
+        <v>-0.1890093669943477</v>
       </c>
       <c r="CX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY19" t="n">
-        <v>0.06214686074564631</v>
+        <v>0.1522769976212315</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-0.01697500711030828</v>
+        <v>0.04884661040198288</v>
       </c>
       <c r="DA19" t="n">
         <v>0</v>
@@ -10993,28 +10993,28 @@
         <v>-0</v>
       </c>
       <c r="DD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>-0.08585076579108387</v>
+        <v>-0.1142413910903867</v>
       </c>
       <c r="DG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.06187019827427667</v>
+        <v>0.03520333795944709</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.00840725719028897</v>
+        <v>-0.09624620189698106</v>
       </c>
       <c r="DJ19" t="n">
         <v>-0</v>
       </c>
       <c r="DK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
@@ -11026,19 +11026,19 @@
         <v>-0</v>
       </c>
       <c r="DO19" t="n">
-        <v>-0.07731138820923494</v>
+        <v>-0.1252518107368351</v>
       </c>
       <c r="DP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ19" t="n">
-        <v>0.01932207722834833</v>
+        <v>-0.05587739118061316</v>
       </c>
       <c r="DR19" t="n">
-        <v>-0.06815593474261998</v>
+        <v>-0.01901474562481241</v>
       </c>
       <c r="DS19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT19" t="n">
         <v>-0</v>
@@ -11053,76 +11053,76 @@
         <v>-0</v>
       </c>
       <c r="DX19" t="n">
-        <v>0.02228776825590621</v>
+        <v>0.1131075959946505</v>
       </c>
       <c r="DY19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ19" t="n">
-        <v>0.000222627228321455</v>
+        <v>0.06857388609472619</v>
       </c>
       <c r="EA19" t="n">
-        <v>-0.07801550723825172</v>
+        <v>-0.04675219118401609</v>
       </c>
       <c r="EB19" t="n">
         <v>0</v>
       </c>
       <c r="EC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED19" t="n">
         <v>0</v>
       </c>
       <c r="EE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG19" t="n">
-        <v>-0.1107924602015831</v>
+        <v>-0.1048479197399531</v>
       </c>
       <c r="EH19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI19" t="n">
-        <v>0.03939501140158397</v>
+        <v>0.07384801061799688</v>
       </c>
       <c r="EJ19" t="n">
-        <v>0.1068332408366498</v>
+        <v>0.06802832333849412</v>
       </c>
       <c r="EK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN19" t="n">
         <v>-0</v>
       </c>
       <c r="EO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP19" t="n">
-        <v>-0.06464088565279016</v>
+        <v>-0.0695213431803431</v>
       </c>
       <c r="EQ19" t="n">
         <v>0</v>
       </c>
       <c r="ER19" t="n">
-        <v>0.04029288570946402</v>
+        <v>0.07439655434568129</v>
       </c>
       <c r="ES19" t="n">
-        <v>0.0146127074824625</v>
+        <v>-0.08157114572026104</v>
       </c>
       <c r="ET19" t="n">
         <v>-0</v>
       </c>
       <c r="EU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV19" t="n">
         <v>0</v>
@@ -11131,46 +11131,46 @@
         <v>-0</v>
       </c>
       <c r="EX19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY19" t="n">
-        <v>-0.1054451589495298</v>
+        <v>-0.2200698334919372</v>
       </c>
       <c r="EZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA19" t="n">
-        <v>0.05129618615524093</v>
+        <v>0.1521982399969704</v>
       </c>
       <c r="FB19" t="n">
-        <v>0.01277143178603117</v>
+        <v>0.02896771413963376</v>
       </c>
       <c r="FC19" t="n">
         <v>-0</v>
       </c>
       <c r="FD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE19" t="n">
         <v>0</v>
       </c>
       <c r="FF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG19" t="n">
         <v>0</v>
       </c>
       <c r="FH19" t="n">
-        <v>-0.01475942373521462</v>
+        <v>-0.1044441774359411</v>
       </c>
       <c r="FI19" t="n">
         <v>-0</v>
       </c>
       <c r="FJ19" t="n">
-        <v>0.08430286278723746</v>
+        <v>0.1240180449885972</v>
       </c>
       <c r="FK19" t="n">
-        <v>-0.07964012069527281</v>
+        <v>0.06630697578419291</v>
       </c>
       <c r="FL19" t="n">
         <v>-0</v>
@@ -11179,31 +11179,31 @@
         <v>0</v>
       </c>
       <c r="FN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ19" t="n">
-        <v>-0.0004307090409562956</v>
+        <v>0.0005515227953308083</v>
       </c>
       <c r="FR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS19" t="n">
-        <v>0.006782966439846424</v>
+        <v>0.1361647077359153</v>
       </c>
       <c r="FT19" t="n">
-        <v>-0.001629290998664996</v>
+        <v>-0.006040197124258893</v>
       </c>
       <c r="FU19" t="n">
         <v>-0</v>
       </c>
       <c r="FV19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW19" t="n">
         <v>0</v>
@@ -11212,31 +11212,31 @@
         <v>0</v>
       </c>
       <c r="FY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ19" t="n">
-        <v>0.02236375163751553</v>
+        <v>-0.1582132501407622</v>
       </c>
       <c r="GA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB19" t="n">
-        <v>-0.04681723576318778</v>
+        <v>0.06762250314180039</v>
       </c>
       <c r="GC19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE19" t="n">
         <v>-0</v>
       </c>
       <c r="GF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
